--- a/reports/Report_43.xlsx
+++ b/reports/Report_43.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\OJT-project-master\OJT-project-master\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D60ED26-47EB-43B3-9789-4C44262B1D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D252D0A-E713-4E7A-8F78-7DE663511816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
